--- a/artfynd/A 46341-2022 artfynd.xlsx
+++ b/artfynd/A 46341-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46341-2022 artfynd.xlsx
+++ b/artfynd/A 46341-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790211</v>
+        <v>96790209</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560670.3511576375</v>
+        <v>560763</v>
       </c>
       <c r="R2" t="n">
-        <v>7108580.926970595</v>
+        <v>7108528</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>130-årig blåbärstallskog</t>
+          <t>140-årig naturskogsartad granskog i nordostsluttning</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,50 +789,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790209</v>
+        <v>112330395</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrakholmberget, Ång</t>
+          <t>Skrakaholmberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560763.3536956087</v>
+        <v>560633</v>
       </c>
       <c r="R3" t="n">
-        <v>7108528.073355105</v>
+        <v>7108638</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,50 +871,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>140-årig naturskogsartad granskog i nordostsluttning</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade granlågor</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>96790210</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560763.3536956087</v>
+        <v>560763</v>
       </c>
       <c r="R4" t="n">
-        <v>7108528.073355105</v>
+        <v>7108528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +958,9 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112330395</v>
+        <v>96790211</v>
       </c>
       <c r="B5" t="n">
-        <v>88221</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,37 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrakaholmberget, Ång</t>
+          <t>Skrakholmberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560633</v>
+        <v>560671</v>
       </c>
       <c r="R5" t="n">
-        <v>7108638</v>
+        <v>7108581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1075,30 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>130-årig blåbärstallskog</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46341-2022 artfynd.xlsx
+++ b/artfynd/A 46341-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790209</t>
         </is>
       </c>
     </row>
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112330395</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,8 +1119,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>